--- a/public/templates/지원정보 양식.xlsx
+++ b/public/templates/지원정보 양식.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>제목 줄입니다. '공고별 지원자 관리' 제목으로 읽을 시트를 찾으니 지우지 마세요.</t>
+          <t>제목 줄입니다. 내용은 읽지 않습니다. 지워도 수험번호 열이 있는 시트를 찾아 읽습니다.</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>나머지 열 모두. 빈 칸이면 그 항목의 검토만 빠집니다.</t>
+          <t>나머지 열 모두. 빈 칸이면 그 항목의 검토만 빠집니다. 검토에 쓰는 열(이름, 학력, 지도교수, 경력, 연구과제)을 지우거나 모두 비워 두면 검토 결과 화면 요약 탭에 무엇이 빠져 어떤 검사를 하지 않았는지 알려 줍니다.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>대학교1~2, 대학원1~3 칸에 하나씩 씁니다. 학교명과 전공명으로 내부위원과 동일학력인지 봅니다.</t>
+          <t>대학교1~2, 대학원1~3 칸에 하나씩 씁니다. 칸이 모자라면 같은 이름 규칙으로 열을 더 만들어도 됩니다(예: 대학교3 - 학교명, 대학교3 - 전공명). 쓰지 않는 칸의 열은 지워도 됩니다. 학교명과 전공명으로 내부위원과 동일학력인지 봅니다.</t>
         </is>
       </c>
     </row>

--- a/public/templates/지원정보 양식.xlsx
+++ b/public/templates/지원정보 양식.xlsx
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -918,184 +918,194 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>모양</t>
+          <t>쓰는 곳</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>채용 사이트(마이다스인)에서 내려받은 지원정보 파일(공고별 지원자 관리)과 같은 머리글입니다. 사이트에서 받은 파일은 고치지 않고 그대로 올리면 됩니다. 이 양식에는 검토가 읽는 열만 남겼습니다.</t>
+          <t>사전스크리닝 검토 &gt; 새 검토 시작의 지원정보 파일. 지원자 학력·경력·연구과제·지도교수로 제척을, 이름·주소로 블라인드 위배를 찾는 데 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>1행</t>
+          <t>모양</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>제목 줄입니다. 내용은 읽지 않습니다. 지워도 수험번호 열이 있는 시트를 찾아 읽습니다.</t>
+          <t>채용 사이트(마이다스인)에서 내려받은 지원정보 파일(공고별 지원자 관리)과 같은 머리글입니다. 사이트에서 받은 파일은 고치지 않고 그대로 올리면 됩니다. 이 양식에는 검토가 읽는 열만 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2행</t>
+          <t>1행</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>머리글 줄입니다. 머리글 이름으로 열을 찾으므로 열 순서는 바뀌어도 되고, 다른 열이 더 있어도 됩니다.</t>
+          <t>제목 줄입니다. 내용은 읽지 않습니다. 지워도 수험번호 열이 있는 시트를 찾아 읽습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>3행부터</t>
+          <t>2행</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>지원자 한 명이 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요.</t>
+          <t>머리글 줄입니다. 머리글 이름으로 열을 찾으므로 열 순서는 바뀌어도 되고, 다른 열이 더 있어도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>꼭 있어야 하는 열</t>
+          <t>3행부터</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>수험번호. 자기소개서 파일의 수험번호와 같아야 그 지원자로 연결됩니다.</t>
+          <t>지원자 한 명이 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>없어도 되는 열</t>
+          <t>꼭 있어야 하는 열</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>나머지 열 모두. 빈 칸이면 그 항목의 검토만 빠집니다. 검토에 쓰는 열(이름, 학력, 지도교수, 경력, 연구과제)을 지우거나 모두 비워 두면 검토 결과 화면 요약 탭에 무엇이 빠져 어떤 검사를 하지 않았는지 알려 줍니다.</t>
+          <t>수험번호. 자기소개서 파일의 수험번호와 같아야 그 지원자로 연결됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>이름·영문이름·한문이름·현주소</t>
+          <t>없어도 되는 열</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>자기소개서와 첨부 실적에 지원자 이름이나 사는 지역이 적혀 있는지 찾는 데 씁니다.</t>
+          <t>나머지 열 모두. 빈 칸이면 그 항목의 검토만 빠집니다. 검토에 쓰는 열(이름, 학력, 지도교수, 경력, 연구과제)을 지우거나 모두 비워 두면 검토 결과 화면 요약 탭에 무엇이 빠져 어떤 검사를 하지 않았는지 알려 줍니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>이름·영문이름·한문이름·현주소</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>대학교1~2, 대학원1~3 칸에 하나씩 씁니다. 칸이 모자라면 같은 이름 규칙으로 열을 더 만들어도 됩니다(예: 대학교3 - 학교명, 대학교3 - 전공명). 쓰지 않는 칸의 열은 지워도 됩니다. 학교명과 전공명으로 내부위원과 동일학력인지 봅니다.</t>
+          <t>자기소개서와 첨부 실적에 지원자 이름이나 사는 지역이 적혀 있는지 찾는 데 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>지도교수</t>
+          <t>학력</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>'대학원 1 : 이름' 처럼 칸 번호와 함께 씁니다. 여러 명이면 줄을 바꿔 씁니다(Alt+Enter). 지도교수가 없으면 '대학원 1 : 해당없음' 으로 씁니다.</t>
+          <t>대학교1~2, 대학원1~3 칸에 하나씩 씁니다. 칸이 모자라면 같은 이름 규칙으로 열을 더 만들어도 됩니다(예: 대학교3 - 학교명, 대학교3 - 전공명). 쓰지 않는 칸의 열은 지워도 됩니다. 학교명·전공명·지도교수가 모두 내부위원과 같으면 동일학력으로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>경력</t>
+          <t>지도교수</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>회사가 여럿이면 한 칸 안에서 줄을 바꿔 씁니다(Alt+Enter). 회사명·재직일자·부서명·직급은 같은 줄끼리 짝이 되므로 줄 수를 맞춰 주세요. 부서명·직급 줄 수가 회사명과 다르면 그 열은 읽지 않습니다.</t>
+          <t>'대학원 1 : 이름' 처럼 칸 번호와 함께 씁니다. 여러 명이면 줄을 바꿔 씁니다(Alt+Enter). 지도교수가 없으면 '대학원 1 : 해당없음' 으로 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>재직일자</t>
+          <t>경력</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>'2018.03.02 ~ 2022.02.28' 모양입니다. 지금 다니고 있으면 '2022.03.02 ~ 재직중' 으로 씁니다.</t>
+          <t>회사가 여럿이면 한 칸 안에서 줄을 바꿔 씁니다(Alt+Enter). 회사명·재직일자·부서명·직급은 같은 줄끼리 짝이 되므로 줄 수를 맞춰 주세요. 부서명·직급 줄 수가 회사명과 다르면 그 열은 읽지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>연구과제</t>
+          <t>재직일자</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>과제가 여럿이면 경력처럼 한 칸 안에서 줄을 바꿔 씁니다. 연구과제명은 연구 목록 파일의 과제명과 대조합니다.</t>
+          <t>'2018.03.02 ~ 2022.02.28' 모양입니다. 지금 다니고 있으면 '2022.03.02 ~ 재직중' 으로 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>연구과제</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2016.02.19, 2016-02-19 모양 모두 읽습니다.</t>
+          <t>과제가 여럿이면 경력처럼 한 칸 안에서 줄을 바꿔 씁니다. 연구과제명은 연구 목록 파일의 과제명과 대조합니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>시트 이름은 상관없습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+          <t>2016.02.19, 2016-02-19 모양 모두 읽습니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>시트 이름은 상관없습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>파일 형식</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>xlsx 또는 xlsm. 암호를 건 엑셀은 올릴 수 없습니다.</t>
         </is>

--- a/public/templates/지원정보 양식.xlsx
+++ b/public/templates/지원정보 양식.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>사전스크리닝 검토 &gt; 새 검토 시작의 지원정보 파일. 지원자 학력·경력·연구과제·지도교수로 제척을, 이름·주소로 블라인드 위배를 찾는 데 씁니다.</t>
+          <t>사전스크리닝 검토 &gt; 신규 검토 생성의 지원정보 파일. 지원자 학력·경력·연구과제·지도교수로 제척을, 이름·주소로 블라인드 위배를 찾는 데 씁니다.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>자기소개서와 첨부 실적에 지원자 이름이나 사는 지역이 적혀 있는지 찾는 데 씁니다.</t>
+          <t>자기소개서에 지원자 이름(한글·영문)이나 사는 지역이, 첨부 실적에 이름(한글·영문·한문)이 적혀 있는지 찾는 데 씁니다.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>대학교1~2, 대학원1~3 칸에 하나씩 씁니다. 칸이 모자라면 같은 이름 규칙으로 열을 더 만들어도 됩니다(예: 대학교3 - 학교명, 대학교3 - 전공명). 쓰지 않는 칸의 열은 지워도 됩니다. 학교명·전공명·지도교수가 모두 내부위원과 같으면 동일학력으로 봅니다.</t>
+          <t>대학교1~2, 대학원1~3 칸에 하나씩 씁니다. 칸이 모자라면 같은 이름 규칙으로 열을 더 만들어도 됩니다(예: 대학교3 - 학교명, 대학교3 - 전공명). 쓰지 않는 칸의 열은 지워도 됩니다. 복수전공은 전공명 칸 안에서 줄을 바꿔 씁니다(Alt+Enter). 쉼표나 / 로 이어 쓰면 한 전공으로 읽습니다. 학교명·지도교수가 내부위원과 같고 전공명도 같으면 동일학력으로 봅니다. 전공명 표기만 다르면 전공명 AI 비교에 올라가고 담당자가 확정합니다.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>'대학원 1 : 이름' 처럼 칸 번호와 함께 씁니다. 여러 명이면 줄을 바꿔 씁니다(Alt+Enter). 지도교수가 없으면 '대학원 1 : 해당없음' 으로 씁니다.</t>
+          <t>'대학원 1 : 이름' 처럼 칸 번호와 함께 이름만 씁니다(교수 같은 호칭 없이). 학력이 여럿이면 줄을 바꿔 칸마다 한 줄씩 씁니다(Alt+Enter. 예: 대학원 1 : 김철수, 다음 줄에 대학원 2 : 이영희). 한 칸에는 지도교수 한 명만 읽습니다. 같은 칸 번호를 두 줄에 쓰면 마지막 줄만, 쉼표로 여러 명을 쓰면 한 이름으로 읽어 동일학력 대조가 되지 않습니다. 지도교수가 없으면 '대학원 1 : 해당없음' 으로 씁니다.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>회사가 여럿이면 한 칸 안에서 줄을 바꿔 씁니다(Alt+Enter). 회사명·재직일자·부서명·직급은 같은 줄끼리 짝이 되므로 줄 수를 맞춰 주세요. 부서명·직급 줄 수가 회사명과 다르면 그 열은 읽지 않습니다.</t>
+          <t>회사가 여럿이면 한 칸 안에서 줄을 바꿔 씁니다(Alt+Enter). 회사명·재직일자·부서명·직급은 같은 줄끼리 짝이 되므로 줄 수를 맞추고 중간에 빈 줄을 두지 마세요. 부서명·직급 줄 수가 회사명과 다르면 그 지원자의 부서명·직급은 읽지 않습니다. 재직일자 줄 수가 다르면 위에서부터 차례로 짝지어 기간이 다른 회사에 붙을 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>'2018.03.02 ~ 2022.02.28' 모양입니다. 지금 다니고 있으면 '2022.03.02 ~ 재직중' 으로 씁니다.</t>
+          <t>'2018.03.02 ~ 2022.02.28' 모양으로 두 날짜 사이에 물결표(~)를 씁니다. 지금 다니고 있으면 '2022.03.02 ~ 재직중' 으로 씁니다('재직 중' 처럼 띄어 쓰면 끝 날짜를 읽지 못합니다).</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>과제가 여럿이면 경력처럼 한 칸 안에서 줄을 바꿔 씁니다. 연구과제명은 연구 목록 파일의 과제명과 대조합니다.</t>
+          <t>과제가 여럿이면 경력처럼 한 칸 안에서 줄을 바꿔 씁니다. 연구과제명·발주기관명·연구기간·참여역할은 같은 줄끼리 짝이 되므로 줄 수를 맞춰 주세요. 발주기관명에 과학기술정책연구원이나 STEPI 가 들어간 과제는 참여과제로 잡고, 연구과제명은 연구 목록 파일의 과제명과 대조합니다.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2016.02.19, 2016-02-19 모양 모두 읽습니다.</t>
+          <t>2016.02.19, 2016-02-19, 2016/02/19 모양과 엑셀 날짜 칸 모두 읽습니다. 20160219 처럼 붙여 쓰거나 16.02.19 처럼 연도를 두 자리로 쓰면 날짜를 잘못 읽습니다.</t>
         </is>
       </c>
     </row>
